--- a/AAII_Financials/Quarterly/MOVE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MOVE_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="92">
   <si>
     <t>MOVE</t>
   </si>
@@ -1609,8 +1609,8 @@
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>3</v>
+      <c r="D23" s="3">
+        <v>-9000</v>
       </c>
       <c r="E23" s="3">
         <v>-7300</v>
@@ -1804,8 +1804,8 @@
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>3</v>
+      <c r="D26" s="3">
+        <v>-9000</v>
       </c>
       <c r="E26" s="3">
         <v>-7300</v>
@@ -1869,8 +1869,8 @@
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>3</v>
+      <c r="D27" s="3">
+        <v>-9000</v>
       </c>
       <c r="E27" s="3">
         <v>-7300</v>
@@ -2259,8 +2259,8 @@
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>3</v>
+      <c r="D33" s="3">
+        <v>-9000</v>
       </c>
       <c r="E33" s="3">
         <v>-7300</v>
@@ -2389,8 +2389,8 @@
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>3</v>
+      <c r="D35" s="3">
+        <v>-9000</v>
       </c>
       <c r="E35" s="3">
         <v>-7300</v>
@@ -2835,7 +2835,7 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>700</v>
+        <v>1300</v>
       </c>
       <c r="E45" s="3">
         <v>1300</v>
@@ -4929,8 +4929,8 @@
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>3</v>
+      <c r="D81" s="3">
+        <v>-9000</v>
       </c>
       <c r="E81" s="3">
         <v>-7300</v>

--- a/AAII_Financials/Quarterly/MOVE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MOVE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="92">
   <si>
     <t>MOVE</t>
   </si>
@@ -656,93 +656,94 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="T7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
@@ -752,31 +753,37 @@
       <c r="W7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E8" s="3">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3">
-        <v>0</v>
+      <c r="D8" s="3">
+        <v>900</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
@@ -817,13 +824,19 @@
       <c r="W8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>3</v>
+      <c r="D9" s="3">
+        <v>1200</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>3</v>
@@ -882,13 +895,19 @@
       <c r="W9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>3</v>
+      <c r="D10" s="3">
+        <v>-300</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>3</v>
@@ -947,8 +966,14 @@
       <c r="W10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -972,62 +997,64 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E12" s="3">
+        <v>3200</v>
+      </c>
+      <c r="F12" s="3">
         <v>5600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>4200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>3900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>5100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>5100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>4100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>4600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>4500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>3800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>3200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>1900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>1900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>6500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>2300</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>1500</v>
       </c>
-      <c r="S12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1037,8 +1064,14 @@
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1102,8 +1135,14 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1116,33 +1155,33 @@
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I14" s="3">
         <v>0</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
+      <c r="J14" s="3">
+        <v>0</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>-400</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1155,11 +1194,11 @@
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="T14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
@@ -1167,8 +1206,14 @@
       <c r="W14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1232,8 +1277,14 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1254,62 +1305,64 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E17" s="3">
+        <v>6000</v>
+      </c>
+      <c r="F17" s="3">
         <v>9100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>7400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>7200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>8000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>8700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>6800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>6900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>6300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>5200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>4700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>3300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>3200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>7900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>2700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>2000</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1319,62 +1372,68 @@
       <c r="W17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E18" s="3">
-        <v>-7400</v>
-      </c>
-      <c r="F18" s="3">
-        <v>-7200</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-8000</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-8700</v>
-      </c>
-      <c r="I18" s="3">
+      <c r="D18" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K18" s="3">
         <v>-6800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-6900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-6300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-5200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-4700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-3300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-3200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-7900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-2700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-2000</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1384,8 +1443,14 @@
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1409,31 +1474,33 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E20" s="3">
-        <v>100</v>
-      </c>
-      <c r="F20" s="3">
-        <v>100</v>
-      </c>
-      <c r="G20" s="3">
-        <v>100</v>
-      </c>
-      <c r="H20" s="3">
-        <v>100</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
+      <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -1445,25 +1512,25 @@
         <v>0</v>
       </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>-1500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-1300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>200</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
+      <c r="T20" s="3">
+        <v>0</v>
       </c>
       <c r="U20" s="3" t="s">
         <v>3</v>
@@ -1474,62 +1541,68 @@
       <c r="W20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E21" s="3">
-        <v>-7200</v>
-      </c>
-      <c r="F21" s="3">
-        <v>-7100</v>
-      </c>
-      <c r="G21" s="3">
-        <v>-7900</v>
-      </c>
-      <c r="H21" s="3">
-        <v>-8600</v>
-      </c>
-      <c r="I21" s="3">
+      <c r="D21" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K21" s="3">
         <v>-6800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-6900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-6300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-5200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-4700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-4700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-4500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-7500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-2600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-2000</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1539,8 +1612,14 @@
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1556,11 +1635,11 @@
       <c r="G22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J22" s="3">
         <v>0</v>
@@ -1575,25 +1654,25 @@
         <v>0</v>
       </c>
       <c r="N22" s="3">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3">
         <v>900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>600</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>200</v>
       </c>
-      <c r="R22" s="3">
-        <v>0</v>
-      </c>
-      <c r="S22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T22" s="3" t="s">
-        <v>3</v>
+      <c r="T22" s="3">
+        <v>0</v>
       </c>
       <c r="U22" s="3" t="s">
         <v>3</v>
@@ -1604,62 +1683,68 @@
       <c r="W22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="F23" s="3">
         <v>-9000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-7300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-7100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-7900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-8600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-6900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-6900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-6300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-5200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-4700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-5600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-4900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-8100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-2700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-2000</v>
       </c>
-      <c r="S23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1669,8 +1754,14 @@
       <c r="W23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1734,8 +1825,14 @@
       <c r="W24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1799,62 +1896,68 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="F26" s="3">
         <v>-9000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-7300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-7100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-7900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-8600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-6900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-6900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-6300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-5200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-4700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-5600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-4900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-8100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-2700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-2000</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1864,62 +1967,68 @@
       <c r="W26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="F27" s="3">
         <v>-9000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-7300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-7100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-7900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-8600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-6900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-6900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-6300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-5200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-4700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-8100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-7400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-14500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-4900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-4000</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1929,8 +2038,14 @@
       <c r="W27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1994,8 +2109,14 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2059,8 +2180,14 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2124,8 +2251,14 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2189,31 +2322,37 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
+      <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
@@ -2225,25 +2364,25 @@
         <v>0</v>
       </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>1500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>1300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-200</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
+      <c r="T32" s="3">
+        <v>0</v>
       </c>
       <c r="U32" s="3" t="s">
         <v>3</v>
@@ -2254,62 +2393,68 @@
       <c r="W32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="F33" s="3">
         <v>-9000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-7300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-7100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-7900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-8600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-6900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-6900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-6300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-5200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-4700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-8100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-7400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-14500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-4900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-4000</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2319,8 +2464,14 @@
       <c r="W33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2384,62 +2535,68 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="F35" s="3">
         <v>-9000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-7300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-7100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-7900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-8600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-6900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-6900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-6300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-5200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-4700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-8100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-7400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-14500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-4900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-4000</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2449,67 +2606,73 @@
       <c r="W35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="T38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2519,8 +2682,14 @@
       <c r="W38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2544,8 +2713,10 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2569,56 +2740,58 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E41" s="3">
+        <v>6100</v>
+      </c>
+      <c r="F41" s="3">
         <v>7700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>14500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>14300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>10800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>15900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>17100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>18400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>17700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>17100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>29300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>46800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>5700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>7600</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2634,8 +2807,14 @@
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2648,33 +2827,33 @@
       <c r="F42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
-      <c r="H42" s="3">
+      <c r="G42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>4200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>9200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>15900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>22200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>13400</v>
       </c>
-      <c r="N42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2687,11 +2866,11 @@
       <c r="S42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T42" s="3">
-        <v>0</v>
-      </c>
-      <c r="U42" s="3">
-        <v>0</v>
+      <c r="T42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V42" s="3">
         <v>0</v>
@@ -2699,40 +2878,46 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="E43" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="F43" s="3">
         <v>300</v>
       </c>
       <c r="G43" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="H43" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="I43" s="3">
         <v>400</v>
       </c>
       <c r="J43" s="3">
+        <v>400</v>
+      </c>
+      <c r="K43" s="3">
+        <v>400</v>
+      </c>
+      <c r="L43" s="3">
         <v>300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>200</v>
-      </c>
-      <c r="L43" s="3">
-        <v>500</v>
-      </c>
-      <c r="M43" s="3">
-        <v>500</v>
       </c>
       <c r="N43" s="3">
         <v>500</v>
@@ -2740,11 +2925,11 @@
       <c r="O43" s="3">
         <v>500</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q43" s="3" t="s">
-        <v>3</v>
+      <c r="P43" s="3">
+        <v>500</v>
+      </c>
+      <c r="Q43" s="3">
+        <v>500</v>
       </c>
       <c r="R43" s="3" t="s">
         <v>3</v>
@@ -2755,40 +2940,46 @@
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U43" s="3">
-        <v>0</v>
-      </c>
-      <c r="V43" s="3">
-        <v>0</v>
+      <c r="U43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+        <v>1100</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2829,56 +3020,62 @@
       <c r="W44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>700</v>
+      </c>
+      <c r="E45" s="3">
+        <v>800</v>
+      </c>
+      <c r="F45" s="3">
         <v>1300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>1300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>900</v>
-      </c>
-      <c r="I45" s="3">
-        <v>1300</v>
-      </c>
-      <c r="J45" s="3">
-        <v>200</v>
       </c>
       <c r="K45" s="3">
         <v>1300</v>
       </c>
       <c r="L45" s="3">
+        <v>200</v>
+      </c>
+      <c r="M45" s="3">
+        <v>1300</v>
+      </c>
+      <c r="N45" s="3">
         <v>1200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>1500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>1900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>700</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2894,56 +3091,62 @@
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E46" s="3">
+        <v>8500</v>
+      </c>
+      <c r="F46" s="3">
         <v>9200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>16100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>15200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>11600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>18100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>23000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>28200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>35100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>41000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>44700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>49200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>6900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>8300</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2959,16 +3162,22 @@
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>700</v>
+        <v>100</v>
       </c>
       <c r="E47" s="3">
-        <v>700</v>
+        <v>200</v>
       </c>
       <c r="F47" s="3">
         <v>700</v>
@@ -2977,34 +3186,34 @@
         <v>700</v>
       </c>
       <c r="H47" s="3">
+        <v>700</v>
+      </c>
+      <c r="I47" s="3">
+        <v>700</v>
+      </c>
+      <c r="J47" s="3">
         <v>400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>600</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
-      </c>
-      <c r="M47" s="3">
-        <v>100</v>
-      </c>
       <c r="N47" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="O47" s="3">
         <v>100</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q47" s="3" t="s">
-        <v>3</v>
+      <c r="P47" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q47" s="3">
+        <v>100</v>
       </c>
       <c r="R47" s="3" t="s">
         <v>3</v>
@@ -3015,25 +3224,31 @@
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U47" s="3">
-        <v>0</v>
-      </c>
-      <c r="V47" s="3">
-        <v>0</v>
+      <c r="U47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="E48" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="F48" s="3">
         <v>400</v>
@@ -3042,10 +3257,10 @@
         <v>400</v>
       </c>
       <c r="H48" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="I48" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="J48" s="3">
         <v>500</v>
@@ -3057,22 +3272,22 @@
         <v>500</v>
       </c>
       <c r="M48" s="3">
+        <v>500</v>
+      </c>
+      <c r="N48" s="3">
+        <v>500</v>
+      </c>
+      <c r="O48" s="3">
         <v>300</v>
       </c>
-      <c r="N48" s="3">
-        <v>0</v>
-      </c>
-      <c r="O48" s="3">
-        <v>0</v>
-      </c>
       <c r="P48" s="3">
         <v>0</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R48" s="3" t="s">
-        <v>3</v>
+      <c r="Q48" s="3">
+        <v>0</v>
+      </c>
+      <c r="R48" s="3">
+        <v>0</v>
       </c>
       <c r="S48" s="3" t="s">
         <v>3</v>
@@ -3089,8 +3304,14 @@
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3154,8 +3375,14 @@
       <c r="W49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3219,8 +3446,14 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3284,13 +3517,19 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="E52" s="3">
         <v>400</v>
@@ -3299,41 +3538,41 @@
         <v>400</v>
       </c>
       <c r="G52" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="H52" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="I52" s="3">
         <v>500</v>
       </c>
       <c r="J52" s="3">
+        <v>500</v>
+      </c>
+      <c r="K52" s="3">
+        <v>500</v>
+      </c>
+      <c r="L52" s="3">
         <v>400</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
-      </c>
-      <c r="L52" s="3">
-        <v>100</v>
-      </c>
       <c r="M52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N52" s="3">
         <v>100</v>
       </c>
       <c r="O52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P52" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q52" s="3">
+        <v>0</v>
+      </c>
+      <c r="R52" s="3">
         <v>400</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3349,8 +3588,14 @@
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3414,56 +3659,62 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E54" s="3">
+        <v>9400</v>
+      </c>
+      <c r="F54" s="3">
         <v>10600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>17600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>16800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>13200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>19500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>24400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>29600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>36300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>41600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>45100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>49400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>7100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>8700</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3479,8 +3730,14 @@
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3504,8 +3761,10 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3529,56 +3788,58 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>3100</v>
+      </c>
+      <c r="F57" s="3">
         <v>2000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>1500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>600</v>
-      </c>
-      <c r="H57" s="3">
-        <v>600</v>
-      </c>
-      <c r="I57" s="3">
-        <v>800</v>
       </c>
       <c r="J57" s="3">
         <v>600</v>
       </c>
       <c r="K57" s="3">
-        <v>300</v>
+        <v>800</v>
       </c>
       <c r="L57" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="M57" s="3">
         <v>300</v>
       </c>
       <c r="N57" s="3">
+        <v>500</v>
+      </c>
+      <c r="O57" s="3">
+        <v>300</v>
+      </c>
+      <c r="P57" s="3">
         <v>400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>200</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3594,31 +3855,37 @@
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
-        <v>0</v>
+      <c r="D58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E58" s="3">
         <v>0</v>
       </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
-      <c r="J58" s="3">
-        <v>0</v>
+      <c r="F58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -3630,20 +3897,20 @@
         <v>0</v>
       </c>
       <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
         <v>300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>200</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3659,56 +3926,62 @@
       <c r="W58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E59" s="3">
+        <v>2800</v>
+      </c>
+      <c r="F59" s="3">
         <v>3600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>3000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>4800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>4400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>3700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>2600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>2000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>2900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>2300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>1500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>1000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>500</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3724,56 +3997,62 @@
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E60" s="3">
+        <v>5900</v>
+      </c>
+      <c r="F60" s="3">
         <v>5500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>4600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>5300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>5000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>4400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>3400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>2600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>3200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>2800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>1800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>1700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>1200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>800</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3789,8 +4068,14 @@
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3828,17 +4113,17 @@
         <v>0</v>
       </c>
       <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3">
         <v>11400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>11100</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -3854,56 +4139,62 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>0</v>
+      </c>
+      <c r="E62" s="3">
+        <v>0</v>
+      </c>
+      <c r="F62" s="3">
         <v>100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>300</v>
-      </c>
-      <c r="L62" s="3">
-        <v>400</v>
-      </c>
-      <c r="M62" s="3">
-        <v>400</v>
       </c>
       <c r="N62" s="3">
         <v>400</v>
       </c>
       <c r="O62" s="3">
+        <v>400</v>
+      </c>
+      <c r="P62" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q62" s="3">
         <v>2500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>700</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3919,8 +4210,14 @@
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3984,8 +4281,14 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4049,8 +4352,14 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4114,56 +4423,62 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>5600</v>
+        <v>6600</v>
       </c>
       <c r="E66" s="3">
-        <v>4700</v>
+        <v>6000</v>
       </c>
       <c r="F66" s="3">
         <v>5600</v>
       </c>
       <c r="G66" s="3">
+        <v>4700</v>
+      </c>
+      <c r="H66" s="3">
+        <v>5600</v>
+      </c>
+      <c r="I66" s="3">
         <v>5300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>4800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>3900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>3100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>3500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>3200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>2200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>2100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>15100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>12600</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4179,8 +4494,14 @@
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4204,8 +4525,10 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4269,8 +4592,14 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4334,8 +4663,14 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4373,17 +4708,17 @@
         <v>0</v>
       </c>
       <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3">
         <v>32800</v>
       </c>
-      <c r="P70" s="3">
+      <c r="R70" s="3">
         <v>30300</v>
       </c>
-      <c r="Q70" s="3">
-        <v>0</v>
-      </c>
-      <c r="R70" s="3">
-        <v>0</v>
-      </c>
       <c r="S70" s="3">
         <v>0</v>
       </c>
@@ -4399,8 +4734,14 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4464,56 +4805,62 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-130100</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-124400</v>
+      </c>
+      <c r="F72" s="3">
         <v>-118400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-109500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-102200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-95100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-87200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-78600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-71700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-64800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-58500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-53300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-48600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-40900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-34200</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4529,8 +4876,14 @@
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4594,8 +4947,14 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4659,8 +5018,14 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4724,56 +5089,62 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E76" s="3">
+        <v>3400</v>
+      </c>
+      <c r="F76" s="3">
         <v>4900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>12800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>11100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>7900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>14700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>20500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>26500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>32700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>38400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>43000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>47300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>-40900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>-34200</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4789,8 +5160,14 @@
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4854,67 +5231,73 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="T80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4924,62 +5307,68 @@
       <c r="W80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="F81" s="3">
         <v>-9000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-7300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-7100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-7900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-8600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-6900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-6900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-6300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-5200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-4700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-8100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-7400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-14500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-4900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-4000</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4989,8 +5378,14 @@
       <c r="W81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5014,13 +5409,15 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E83" s="3">
         <v>0</v>
@@ -5064,11 +5461,11 @@
       <c r="R83" s="3">
         <v>0</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T83" s="3" t="s">
-        <v>3</v>
+      <c r="S83" s="3">
+        <v>0</v>
+      </c>
+      <c r="T83" s="3">
+        <v>0</v>
       </c>
       <c r="U83" s="3" t="s">
         <v>3</v>
@@ -5079,8 +5476,14 @@
       <c r="W83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5144,8 +5547,14 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5209,8 +5618,14 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5274,8 +5689,14 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5339,8 +5760,14 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5404,62 +5831,68 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="F89" s="3">
         <v>-7000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-7900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-6100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-6300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-6400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-6400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-5800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-5100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-3300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-3700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-4000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-2500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-8100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-2200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-2200</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5469,8 +5902,14 @@
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5494,8 +5933,10 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5521,22 +5962,22 @@
         <v>0</v>
       </c>
       <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
         <v>-200</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
         <v>-300</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
-      <c r="O91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P91" s="3" t="s">
-        <v>3</v>
+      <c r="P91" s="3">
+        <v>0</v>
       </c>
       <c r="Q91" s="3" t="s">
         <v>3</v>
@@ -5550,17 +5991,23 @@
       <c r="T91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
-      </c>
-      <c r="V91" s="3">
-        <v>0</v>
+      <c r="U91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5624,8 +6071,14 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5689,8 +6142,14 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5704,32 +6163,32 @@
         <v>0</v>
       </c>
       <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
         <v>800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>3400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>5000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>6500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>5900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-8900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-13700</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
       <c r="P94" s="3">
         <v>0</v>
       </c>
@@ -5739,11 +6198,11 @@
       <c r="R94" s="3">
         <v>0</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T94" s="3" t="s">
-        <v>3</v>
+      <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3">
+        <v>0</v>
       </c>
       <c r="U94" s="3" t="s">
         <v>3</v>
@@ -5754,8 +6213,14 @@
       <c r="W94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5779,8 +6244,10 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5844,8 +6311,14 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5909,8 +6382,14 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5974,8 +6453,14 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6039,8 +6524,14 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -6048,53 +6539,53 @@
         <v>200</v>
       </c>
       <c r="E100" s="3">
+        <v>3700</v>
+      </c>
+      <c r="F100" s="3">
+        <v>200</v>
+      </c>
+      <c r="G100" s="3">
         <v>8100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>9600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>1900</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>-200</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>45100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>11400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>7000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>1200</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6104,8 +6595,14 @@
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6169,62 +6666,68 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="F102" s="3">
         <v>-6800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>3500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-5200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-1100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-1400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-12200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-17400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>41000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-1900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>3300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>4700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-1000</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6232,6 +6735,12 @@
         <v>3</v>
       </c>
       <c r="W102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MOVE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MOVE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="92">
   <si>
     <t>MOVE</t>
   </si>
@@ -656,97 +656,98 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
@@ -759,17 +760,20 @@
       <c r="Y7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="3">
         <v>900</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F8" s="3" t="s">
         <v>3</v>
       </c>
@@ -785,8 +789,8 @@
       <c r="J8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K8" s="3">
-        <v>0</v>
+      <c r="K8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L8" s="3">
         <v>0</v>
@@ -830,17 +834,20 @@
       <c r="Y8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>400</v>
+      </c>
+      <c r="E9" s="3">
         <v>1200</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F9" s="3" t="s">
         <v>3</v>
       </c>
@@ -901,17 +908,20 @@
       <c r="Y9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E10" s="3">
         <v>-300</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F10" s="3" t="s">
         <v>3</v>
       </c>
@@ -972,8 +982,11 @@
       <c r="Y10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -999,8 +1012,9 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1008,56 +1022,56 @@
         <v>2900</v>
       </c>
       <c r="E12" s="3">
+        <v>2900</v>
+      </c>
+      <c r="F12" s="3">
         <v>3200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>5600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>4200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>3900</v>
-      </c>
-      <c r="I12" s="3">
-        <v>5100</v>
       </c>
       <c r="J12" s="3">
         <v>5100</v>
       </c>
       <c r="K12" s="3">
+        <v>5100</v>
+      </c>
+      <c r="L12" s="3">
         <v>4100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>4600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>4500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>3800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>3200</v>
-      </c>
-      <c r="P12" s="3">
-        <v>1900</v>
       </c>
       <c r="Q12" s="3">
         <v>1900</v>
       </c>
       <c r="R12" s="3">
+        <v>1900</v>
+      </c>
+      <c r="S12" s="3">
         <v>6500</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>2300</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>1500</v>
       </c>
-      <c r="U12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1070,8 +1084,11 @@
       <c r="Y12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1141,8 +1158,11 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1161,8 +1181,8 @@
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J14" s="3">
         <v>0</v>
@@ -1170,21 +1190,21 @@
       <c r="K14" s="3">
         <v>0</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>-400</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1200,8 +1220,8 @@
       <c r="U14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="V14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
@@ -1212,8 +1232,11 @@
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1283,8 +1306,11 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1307,65 +1333,66 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E17" s="3">
         <v>6600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>6000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>9100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>7400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>7200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>8000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>8700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>6800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>6900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>6300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>5200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>7900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2000</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1378,17 +1405,20 @@
       <c r="Y17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E18" s="3">
         <v>-5700</v>
       </c>
-      <c r="E18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1404,39 +1434,39 @@
       <c r="J18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K18" s="3">
+      <c r="K18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L18" s="3">
         <v>-6800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-6900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-6300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-5200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-4700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-3200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-7900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-2700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-2000</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1449,8 +1479,11 @@
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1476,16 +1509,17 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>3</v>
+      <c r="D20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="3">
+        <v>0</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>3</v>
@@ -1502,8 +1536,8 @@
       <c r="J20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
+      <c r="K20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L20" s="3">
         <v>0</v>
@@ -1518,22 +1552,22 @@
         <v>0</v>
       </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>200</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
+      <c r="U20" s="3">
+        <v>0</v>
       </c>
       <c r="V20" s="3" t="s">
         <v>3</v>
@@ -1547,17 +1581,20 @@
       <c r="Y20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3">
+      <c r="D21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E21" s="3">
         <v>-5700</v>
       </c>
-      <c r="E21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1573,39 +1610,39 @@
       <c r="J21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K21" s="3">
+      <c r="K21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L21" s="3">
         <v>-6800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-6900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-6300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-5200</v>
-      </c>
-      <c r="O21" s="3">
-        <v>-4700</v>
       </c>
       <c r="P21" s="3">
         <v>-4700</v>
       </c>
       <c r="Q21" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="R21" s="3">
         <v>-4500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-7500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-2600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-2000</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1618,28 +1655,31 @@
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>3</v>
+      <c r="D22" s="3">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3">
+        <v>0</v>
       </c>
       <c r="J22" s="3">
         <v>0</v>
@@ -1660,22 +1700,22 @@
         <v>0</v>
       </c>
       <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3">
         <v>900</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>600</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>200</v>
       </c>
-      <c r="T22" s="3">
-        <v>0</v>
-      </c>
-      <c r="U22" s="3" t="s">
-        <v>3</v>
+      <c r="U22" s="3">
+        <v>0</v>
       </c>
       <c r="V22" s="3" t="s">
         <v>3</v>
@@ -1689,65 +1729,68 @@
       <c r="Y22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-5700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-6000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-9000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-7300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-7100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-7900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-8600</v>
-      </c>
-      <c r="K23" s="3">
-        <v>-6900</v>
       </c>
       <c r="L23" s="3">
         <v>-6900</v>
       </c>
       <c r="M23" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="N23" s="3">
         <v>-6300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-5200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-4700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-5600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-4900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-8100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-2700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-2000</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1760,8 +1803,11 @@
       <c r="Y23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1831,8 +1877,11 @@
       <c r="Y24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1902,65 +1951,68 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-5700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-6000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-9000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-7300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-7100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-7900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-8600</v>
-      </c>
-      <c r="K26" s="3">
-        <v>-6900</v>
       </c>
       <c r="L26" s="3">
         <v>-6900</v>
       </c>
       <c r="M26" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="N26" s="3">
         <v>-6300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-5200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-4700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-5600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-4900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-8100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-2700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-2000</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1973,65 +2025,68 @@
       <c r="Y26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-5700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-6000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-9000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-7300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-7100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-7900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-8600</v>
-      </c>
-      <c r="K27" s="3">
-        <v>-6900</v>
       </c>
       <c r="L27" s="3">
         <v>-6900</v>
       </c>
       <c r="M27" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="N27" s="3">
         <v>-6300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-5200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-4700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-8100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-7400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-14500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-4900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-4000</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2044,8 +2099,11 @@
       <c r="Y27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2115,8 +2173,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2186,8 +2247,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2257,8 +2321,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2328,16 +2395,19 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>0</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>3</v>
+      <c r="D32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E32" s="3">
+        <v>0</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>3</v>
@@ -2354,8 +2424,8 @@
       <c r="J32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
+      <c r="K32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L32" s="3">
         <v>0</v>
@@ -2370,22 +2440,22 @@
         <v>0</v>
       </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>1500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-200</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
+      <c r="U32" s="3">
+        <v>0</v>
       </c>
       <c r="V32" s="3" t="s">
         <v>3</v>
@@ -2399,65 +2469,68 @@
       <c r="Y32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-5700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-6000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-9000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-7300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-7100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-7900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-8600</v>
-      </c>
-      <c r="K33" s="3">
-        <v>-6900</v>
       </c>
       <c r="L33" s="3">
         <v>-6900</v>
       </c>
       <c r="M33" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="N33" s="3">
         <v>-6300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-5200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-4700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-8100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-7400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-14500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-4900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-4000</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2470,8 +2543,11 @@
       <c r="Y33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2541,65 +2617,68 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-5700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-6000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-9000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-7300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-7100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-7900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-8600</v>
-      </c>
-      <c r="K35" s="3">
-        <v>-6900</v>
       </c>
       <c r="L35" s="3">
         <v>-6900</v>
       </c>
       <c r="M35" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="N35" s="3">
         <v>-6300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-5200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-4700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-8100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-7400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-14500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-4900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-4000</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2612,70 +2691,73 @@
       <c r="Y35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2688,8 +2770,11 @@
       <c r="Y38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2715,8 +2800,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2742,59 +2828,60 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>16900</v>
+      </c>
+      <c r="E41" s="3">
         <v>2100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>6100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>7700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>14500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>14300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>10800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>15900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>17100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>18400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>17700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>17100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>29300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>46800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>5700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>7600</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2813,8 +2900,11 @@
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2833,30 +2923,30 @@
       <c r="H42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
+      <c r="I42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>4200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>9200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>15900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>22200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>13400</v>
       </c>
-      <c r="P42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2872,8 +2962,8 @@
       <c r="U42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V42" s="3">
-        <v>0</v>
+      <c r="V42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W42" s="3">
         <v>0</v>
@@ -2884,19 +2974,22 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="E43" s="3">
         <v>500</v>
       </c>
       <c r="F43" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="G43" s="3">
         <v>300</v>
@@ -2905,7 +2998,7 @@
         <v>300</v>
       </c>
       <c r="I43" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="J43" s="3">
         <v>400</v>
@@ -2914,13 +3007,13 @@
         <v>400</v>
       </c>
       <c r="L43" s="3">
+        <v>400</v>
+      </c>
+      <c r="M43" s="3">
         <v>300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>200</v>
-      </c>
-      <c r="N43" s="3">
-        <v>500</v>
       </c>
       <c r="O43" s="3">
         <v>500</v>
@@ -2931,8 +3024,8 @@
       <c r="Q43" s="3">
         <v>500</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>3</v>
+      <c r="R43" s="3">
+        <v>500</v>
       </c>
       <c r="S43" s="3" t="s">
         <v>3</v>
@@ -2946,8 +3039,8 @@
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W43" s="3">
-        <v>0</v>
+      <c r="W43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X43" s="3">
         <v>0</v>
@@ -2955,19 +3048,22 @@
       <c r="Y43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>1100</v>
+        <v>1800</v>
       </c>
       <c r="E44" s="3">
         <v>1100</v>
       </c>
-      <c r="F44" s="3" t="s">
-        <v>3</v>
+      <c r="F44" s="3">
+        <v>1100</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>3</v>
@@ -2981,8 +3077,8 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -3026,58 +3122,61 @@
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>800</v>
+      </c>
+      <c r="E45" s="3">
         <v>700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>800</v>
-      </c>
-      <c r="F45" s="3">
-        <v>1300</v>
       </c>
       <c r="G45" s="3">
         <v>1300</v>
       </c>
       <c r="H45" s="3">
+        <v>1300</v>
+      </c>
+      <c r="I45" s="3">
         <v>700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1900</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>700</v>
       </c>
       <c r="R45" s="3">
         <v>700</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
+      <c r="S45" s="3">
+        <v>700</v>
       </c>
       <c r="T45" s="3" t="s">
         <v>3</v>
@@ -3097,59 +3196,62 @@
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>19700</v>
+      </c>
+      <c r="E46" s="3">
         <v>4400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>8500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>9200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>16100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>15200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>11600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>18100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>23000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>28200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>35100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>41000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>44700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>49200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>6900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>8300</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3168,8 +3270,11 @@
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3177,10 +3282,10 @@
         <v>100</v>
       </c>
       <c r="E47" s="3">
+        <v>100</v>
+      </c>
+      <c r="F47" s="3">
         <v>200</v>
-      </c>
-      <c r="F47" s="3">
-        <v>700</v>
       </c>
       <c r="G47" s="3">
         <v>700</v>
@@ -3192,32 +3297,32 @@
         <v>700</v>
       </c>
       <c r="J47" s="3">
-        <v>400</v>
+        <v>700</v>
       </c>
       <c r="K47" s="3">
         <v>400</v>
       </c>
       <c r="L47" s="3">
+        <v>400</v>
+      </c>
+      <c r="M47" s="3">
         <v>500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>600</v>
       </c>
-      <c r="N47" s="3">
-        <v>0</v>
-      </c>
       <c r="O47" s="3">
+        <v>0</v>
+      </c>
+      <c r="P47" s="3">
         <v>100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>100</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3230,8 +3335,8 @@
       <c r="V47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W47" s="3">
-        <v>0</v>
+      <c r="W47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X47" s="3">
         <v>0</v>
@@ -3239,8 +3344,11 @@
       <c r="Y47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3251,7 +3359,7 @@
         <v>300</v>
       </c>
       <c r="F48" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="G48" s="3">
         <v>400</v>
@@ -3263,7 +3371,7 @@
         <v>400</v>
       </c>
       <c r="J48" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="K48" s="3">
         <v>500</v>
@@ -3278,19 +3386,19 @@
         <v>500</v>
       </c>
       <c r="O48" s="3">
+        <v>500</v>
+      </c>
+      <c r="P48" s="3">
         <v>300</v>
       </c>
-      <c r="P48" s="3">
-        <v>0</v>
-      </c>
       <c r="Q48" s="3">
         <v>0</v>
       </c>
       <c r="R48" s="3">
         <v>0</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>3</v>
+      <c r="S48" s="3">
+        <v>0</v>
       </c>
       <c r="T48" s="3" t="s">
         <v>3</v>
@@ -3310,8 +3418,11 @@
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3381,8 +3492,11 @@
       <c r="Y49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3452,8 +3566,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3523,16 +3640,19 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>800</v>
+      </c>
+      <c r="E52" s="3">
         <v>300</v>
-      </c>
-      <c r="E52" s="3">
-        <v>400</v>
       </c>
       <c r="F52" s="3">
         <v>400</v>
@@ -3544,7 +3664,7 @@
         <v>400</v>
       </c>
       <c r="I52" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="J52" s="3">
         <v>500</v>
@@ -3553,13 +3673,13 @@
         <v>500</v>
       </c>
       <c r="L52" s="3">
+        <v>500</v>
+      </c>
+      <c r="M52" s="3">
         <v>400</v>
       </c>
-      <c r="M52" s="3">
-        <v>0</v>
-      </c>
       <c r="N52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O52" s="3">
         <v>100</v>
@@ -3568,14 +3688,14 @@
         <v>100</v>
       </c>
       <c r="Q52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R52" s="3">
+        <v>0</v>
+      </c>
+      <c r="S52" s="3">
         <v>400</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3594,8 +3714,11 @@
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3665,59 +3788,62 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>20800</v>
+      </c>
+      <c r="E54" s="3">
         <v>5100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>9400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>10600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>17600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>16800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>13200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>19500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>24400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>29600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>36300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>41600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>45100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>49400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>7100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>8700</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3736,8 +3862,11 @@
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3763,8 +3892,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3790,58 +3920,59 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E57" s="3">
         <v>4000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>500</v>
-      </c>
-      <c r="I57" s="3">
-        <v>600</v>
       </c>
       <c r="J57" s="3">
         <v>600</v>
       </c>
       <c r="K57" s="3">
+        <v>600</v>
+      </c>
+      <c r="L57" s="3">
         <v>800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>400</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>200</v>
       </c>
       <c r="R57" s="3">
         <v>200</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>3</v>
+      <c r="S57" s="3">
+        <v>200</v>
       </c>
       <c r="T57" s="3" t="s">
         <v>3</v>
@@ -3861,19 +3992,22 @@
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E58" s="3">
-        <v>0</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>3</v>
+      <c r="D58" s="3">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F58" s="3">
+        <v>0</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>3</v>
@@ -3887,8 +4021,8 @@
       <c r="J58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
+      <c r="K58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L58" s="3">
         <v>0</v>
@@ -3903,16 +4037,16 @@
         <v>0</v>
       </c>
       <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3">
         <v>300</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>200</v>
       </c>
       <c r="R58" s="3">
         <v>200</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>3</v>
+      <c r="S58" s="3">
+        <v>200</v>
       </c>
       <c r="T58" s="3" t="s">
         <v>3</v>
@@ -3932,59 +4066,62 @@
       <c r="Y58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E59" s="3">
         <v>2600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>4800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>4400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>500</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4003,59 +4140,62 @@
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E60" s="3">
         <v>6600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>5900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>5500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>4600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>5300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>5000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>4400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>800</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4074,8 +4214,11 @@
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4119,14 +4262,14 @@
         <v>0</v>
       </c>
       <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3">
         <v>11400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>11100</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
@@ -4145,43 +4288,46 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="E62" s="3">
         <v>0</v>
       </c>
       <c r="F62" s="3">
+        <v>0</v>
+      </c>
+      <c r="G62" s="3">
         <v>100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>300</v>
-      </c>
-      <c r="I62" s="3">
-        <v>400</v>
       </c>
       <c r="J62" s="3">
         <v>400</v>
       </c>
       <c r="K62" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="L62" s="3">
         <v>500</v>
       </c>
       <c r="M62" s="3">
+        <v>500</v>
+      </c>
+      <c r="N62" s="3">
         <v>300</v>
-      </c>
-      <c r="N62" s="3">
-        <v>400</v>
       </c>
       <c r="O62" s="3">
         <v>400</v>
@@ -4190,14 +4336,14 @@
         <v>400</v>
       </c>
       <c r="Q62" s="3">
+        <v>400</v>
+      </c>
+      <c r="R62" s="3">
         <v>2500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>700</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4216,8 +4362,11 @@
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4287,8 +4436,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4358,8 +4510,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4429,59 +4584,62 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E66" s="3">
         <v>6600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>6000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>15100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>12600</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4500,8 +4658,11 @@
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4527,8 +4688,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4598,8 +4760,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4669,8 +4834,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4714,14 +4882,14 @@
         <v>0</v>
       </c>
       <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3">
         <v>32800</v>
       </c>
-      <c r="R70" s="3">
+      <c r="S70" s="3">
         <v>30300</v>
       </c>
-      <c r="S70" s="3">
-        <v>0</v>
-      </c>
       <c r="T70" s="3">
         <v>0</v>
       </c>
@@ -4740,8 +4908,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4811,59 +4982,62 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-136300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-130100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-124400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-118400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-109500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-102200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-95100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-87200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-78600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-71700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-64800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-58500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-53300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-48600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-40900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-34200</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4882,8 +5056,11 @@
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4953,8 +5130,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5024,8 +5204,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5095,59 +5278,62 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>16800</v>
+      </c>
+      <c r="E76" s="3">
         <v>-1500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>12800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>11100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>7900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>14700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>20500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>26500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>32700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>38400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>43000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>47300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-40900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-34200</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5166,8 +5352,11 @@
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5237,70 +5426,73 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5313,65 +5505,68 @@
       <c r="Y80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-5700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-6000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-9000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-7300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-7100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-7900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-8600</v>
-      </c>
-      <c r="K81" s="3">
-        <v>-6900</v>
       </c>
       <c r="L81" s="3">
         <v>-6900</v>
       </c>
       <c r="M81" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="N81" s="3">
         <v>-6300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-5200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-4700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-8100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-7400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-14500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-4900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-4000</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5384,8 +5579,11 @@
       <c r="Y81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5411,17 +5609,18 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>0</v>
+      </c>
+      <c r="E83" s="3">
         <v>100</v>
       </c>
-      <c r="E83" s="3">
-        <v>0</v>
-      </c>
       <c r="F83" s="3">
         <v>0</v>
       </c>
@@ -5467,8 +5666,8 @@
       <c r="T83" s="3">
         <v>0</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>3</v>
+      <c r="U83" s="3">
+        <v>0</v>
       </c>
       <c r="V83" s="3" t="s">
         <v>3</v>
@@ -5482,8 +5681,11 @@
       <c r="Y83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5553,8 +5755,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5624,8 +5829,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5695,8 +5903,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5766,8 +5977,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5837,64 +6051,67 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-4100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-5200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-7000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-7900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-6100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-6300</v>
-      </c>
-      <c r="J89" s="3">
-        <v>-6400</v>
       </c>
       <c r="K89" s="3">
         <v>-6400</v>
       </c>
       <c r="L89" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="M89" s="3">
         <v>-5800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-5100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-3300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-3700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-4000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-2500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-8100</v>
-      </c>
-      <c r="S89" s="3">
-        <v>-2200</v>
       </c>
       <c r="T89" s="3">
         <v>-2200</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>3</v>
+      <c r="U89" s="3">
+        <v>-2200</v>
       </c>
       <c r="V89" s="3" t="s">
         <v>3</v>
@@ -5908,8 +6125,11 @@
       <c r="Y89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5935,8 +6155,9 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5968,19 +6189,19 @@
         <v>0</v>
       </c>
       <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
         <v>-200</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
       <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
         <v>-300</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q91" s="3" t="s">
-        <v>3</v>
+      <c r="Q91" s="3">
+        <v>0</v>
       </c>
       <c r="R91" s="3" t="s">
         <v>3</v>
@@ -5997,8 +6218,8 @@
       <c r="V91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W91" s="3">
-        <v>0</v>
+      <c r="W91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X91" s="3">
         <v>0</v>
@@ -6006,8 +6227,11 @@
       <c r="Y91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6077,8 +6301,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6148,8 +6375,11 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -6169,29 +6399,29 @@
         <v>0</v>
       </c>
       <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
         <v>800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>3400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>5000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>6500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>5900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-8900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-13700</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
       <c r="Q94" s="3">
         <v>0</v>
       </c>
@@ -6204,8 +6434,8 @@
       <c r="T94" s="3">
         <v>0</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>3</v>
+      <c r="U94" s="3">
+        <v>0</v>
       </c>
       <c r="V94" s="3" t="s">
         <v>3</v>
@@ -6219,8 +6449,11 @@
       <c r="Y94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6246,8 +6479,9 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6317,8 +6551,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6388,8 +6625,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6459,8 +6699,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6530,65 +6773,68 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>22900</v>
+      </c>
+      <c r="E100" s="3">
         <v>200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>3700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>8100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>9600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1900</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
         <v>0</v>
       </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>-200</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
       <c r="O100" s="3">
         <v>0</v>
       </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>45100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>11400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>7000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>1200</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6601,8 +6847,11 @@
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6672,65 +6921,68 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>14700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-4000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-6800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>3500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-5200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-12200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-17400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>41000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>3300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>4700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-1000</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6741,6 +6993,9 @@
         <v>3</v>
       </c>
       <c r="Y102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MOVE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MOVE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="92">
   <si>
     <t>MOVE</t>
   </si>
@@ -656,101 +656,102 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W7" s="2" t="s">
         <v>3</v>
       </c>
@@ -763,20 +764,23 @@
       <c r="Z7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="3">
         <v>900</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G8" s="3" t="s">
         <v>3</v>
       </c>
@@ -792,8 +796,8 @@
       <c r="K8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L8" s="3">
-        <v>0</v>
+      <c r="L8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M8" s="3">
         <v>0</v>
@@ -837,20 +841,23 @@
       <c r="Z8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>800</v>
+      </c>
+      <c r="E9" s="3">
         <v>400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1200</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G9" s="3" t="s">
         <v>3</v>
       </c>
@@ -911,19 +918,22 @@
       <c r="Z9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>3</v>
+      <c r="D10" s="3">
+        <v>-800</v>
       </c>
       <c r="E10" s="3">
-        <v>-300</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>3</v>
+        <v>-400</v>
+      </c>
+      <c r="F10" s="3">
+        <v>-400</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>3</v>
@@ -985,8 +995,11 @@
       <c r="Z10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1013,68 +1026,69 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>2900</v>
+        <v>3400</v>
       </c>
       <c r="E12" s="3">
         <v>2900</v>
       </c>
       <c r="F12" s="3">
-        <v>3200</v>
+        <v>2900</v>
       </c>
       <c r="G12" s="3">
+        <v>3100</v>
+      </c>
+      <c r="H12" s="3">
         <v>5600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>4200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>3900</v>
-      </c>
-      <c r="J12" s="3">
-        <v>5100</v>
       </c>
       <c r="K12" s="3">
         <v>5100</v>
       </c>
       <c r="L12" s="3">
+        <v>5100</v>
+      </c>
+      <c r="M12" s="3">
         <v>4100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>4600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>4500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>3800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>3200</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>1900</v>
       </c>
       <c r="R12" s="3">
         <v>1900</v>
       </c>
       <c r="S12" s="3">
+        <v>1900</v>
+      </c>
+      <c r="T12" s="3">
         <v>6500</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>2300</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>1500</v>
       </c>
-      <c r="V12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1087,8 +1101,11 @@
       <c r="Z12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1161,8 +1178,11 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1184,8 +1204,8 @@
       <c r="I14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1193,21 +1213,21 @@
       <c r="L14" s="3">
         <v>0</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>-400</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1223,8 +1243,8 @@
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
+      <c r="W14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X14" s="3">
         <v>0</v>
@@ -1235,8 +1255,11 @@
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1247,7 +1270,7 @@
         <v>0</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G15" s="3">
         <v>0</v>
@@ -1309,8 +1332,11 @@
       <c r="Z15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1334,68 +1360,69 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E17" s="3">
         <v>6400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>6600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>6000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>9100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>7400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>7200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>8000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>8700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>6800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>6900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>6300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>5200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>7900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2000</v>
       </c>
-      <c r="V17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1408,68 +1435,71 @@
       <c r="Z17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>3</v>
+      <c r="D18" s="3">
+        <v>-7400</v>
       </c>
       <c r="E18" s="3">
-        <v>-5700</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>3</v>
+        <v>-6400</v>
+      </c>
+      <c r="F18" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="G18" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="H18" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-7200</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L18" s="3">
+      <c r="L18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M18" s="3">
         <v>-6800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-6900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-6300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-5200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-4700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-3300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-3200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-7900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-2700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-2000</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1482,8 +1512,11 @@
       <c r="Z18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1510,16 +1543,17 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
+      <c r="E20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>3</v>
@@ -1539,8 +1573,8 @@
       <c r="K20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
+      <c r="L20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M20" s="3">
         <v>0</v>
@@ -1555,22 +1589,22 @@
         <v>0</v>
       </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>-1500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>200</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
-      <c r="V20" s="3" t="s">
-        <v>3</v>
+      <c r="V20" s="3">
+        <v>0</v>
       </c>
       <c r="W20" s="3" t="s">
         <v>3</v>
@@ -1584,68 +1618,71 @@
       <c r="Z20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>3</v>
+      <c r="D21" s="3">
+        <v>-7300</v>
       </c>
       <c r="E21" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="F21" s="3">
         <v>-5700</v>
       </c>
-      <c r="F21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
+      <c r="G21" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-7200</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L21" s="3">
+      <c r="L21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M21" s="3">
         <v>-6800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-6900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-6300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-5200</v>
-      </c>
-      <c r="P21" s="3">
-        <v>-4700</v>
       </c>
       <c r="Q21" s="3">
         <v>-4700</v>
       </c>
       <c r="R21" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="S21" s="3">
         <v>-4500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-7500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-2600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-2000</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1658,31 +1695,34 @@
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1703,22 +1743,22 @@
         <v>0</v>
       </c>
       <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3">
         <v>900</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>600</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>200</v>
       </c>
-      <c r="U22" s="3">
-        <v>0</v>
-      </c>
-      <c r="V22" s="3" t="s">
-        <v>3</v>
+      <c r="V22" s="3">
+        <v>0</v>
       </c>
       <c r="W22" s="3" t="s">
         <v>3</v>
@@ -1732,68 +1772,71 @@
       <c r="Z22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-6200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-5700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-6000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-9000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-7300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-7100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-7900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-8600</v>
-      </c>
-      <c r="L23" s="3">
-        <v>-6900</v>
       </c>
       <c r="M23" s="3">
         <v>-6900</v>
       </c>
       <c r="N23" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="O23" s="3">
         <v>-6300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-5200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-4700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-5600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-4900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-8100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-2700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-2000</v>
       </c>
-      <c r="V23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1806,31 +1849,34 @@
       <c r="Z23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -1880,8 +1926,11 @@
       <c r="Z24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1954,68 +2003,71 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-6200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-5700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-6000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-9000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-7300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-7100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-7900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-8600</v>
-      </c>
-      <c r="L26" s="3">
-        <v>-6900</v>
       </c>
       <c r="M26" s="3">
         <v>-6900</v>
       </c>
       <c r="N26" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="O26" s="3">
         <v>-6300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-5200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-4700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-5600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-4900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-8100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-2700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-2000</v>
       </c>
-      <c r="V26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2028,68 +2080,71 @@
       <c r="Z26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-6200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-5700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-6000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-9000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-7300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-7100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-7900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-8600</v>
-      </c>
-      <c r="L27" s="3">
-        <v>-6900</v>
       </c>
       <c r="M27" s="3">
         <v>-6900</v>
       </c>
       <c r="N27" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="O27" s="3">
         <v>-6300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-5200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-4700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-8100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-7400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-14500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-4900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-4000</v>
       </c>
-      <c r="V27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2102,8 +2157,11 @@
       <c r="Z27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2176,8 +2234,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2250,8 +2311,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2324,8 +2388,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2398,16 +2465,19 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
+      <c r="E32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>3</v>
@@ -2427,8 +2497,8 @@
       <c r="K32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
+      <c r="L32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M32" s="3">
         <v>0</v>
@@ -2443,22 +2513,22 @@
         <v>0</v>
       </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>1500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-200</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
-      <c r="V32" s="3" t="s">
-        <v>3</v>
+      <c r="V32" s="3">
+        <v>0</v>
       </c>
       <c r="W32" s="3" t="s">
         <v>3</v>
@@ -2472,68 +2542,71 @@
       <c r="Z32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-6200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-5700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-6000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-9000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-7300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-7100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-7900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-8600</v>
-      </c>
-      <c r="L33" s="3">
-        <v>-6900</v>
       </c>
       <c r="M33" s="3">
         <v>-6900</v>
       </c>
       <c r="N33" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="O33" s="3">
         <v>-6300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-5200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-4700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-8100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-7400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-14500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-4900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-4000</v>
       </c>
-      <c r="V33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2546,8 +2619,11 @@
       <c r="Z33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2620,68 +2696,71 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-6200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-5700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-6000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-9000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-7300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-7100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-7900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-8600</v>
-      </c>
-      <c r="L35" s="3">
-        <v>-6900</v>
       </c>
       <c r="M35" s="3">
         <v>-6900</v>
       </c>
       <c r="N35" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="O35" s="3">
         <v>-6300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-5200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-4700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-8100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-7400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-14500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-4900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-4000</v>
       </c>
-      <c r="V35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2694,73 +2773,76 @@
       <c r="Z35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2773,8 +2855,11 @@
       <c r="Z38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2801,8 +2886,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2829,62 +2915,63 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>11300</v>
+      </c>
+      <c r="E41" s="3">
         <v>16900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>6100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>7700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>14500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>14300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>10800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>15900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>17100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>18400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>17700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>17100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>29300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>46800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>5700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>7600</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2903,53 +2990,56 @@
       <c r="Z41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>3</v>
+      <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
       </c>
       <c r="J42" s="3">
         <v>0</v>
       </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>4200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>9200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>15900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>22200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>13400</v>
       </c>
-      <c r="Q42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2965,8 +3055,8 @@
       <c r="V42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W42" s="3">
-        <v>0</v>
+      <c r="W42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X42" s="3">
         <v>0</v>
@@ -2977,8 +3067,11 @@
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2986,13 +3079,13 @@
         <v>200</v>
       </c>
       <c r="E43" s="3">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="F43" s="3">
         <v>500</v>
       </c>
       <c r="G43" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="H43" s="3">
         <v>300</v>
@@ -3001,7 +3094,7 @@
         <v>300</v>
       </c>
       <c r="J43" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="K43" s="3">
         <v>400</v>
@@ -3010,13 +3103,13 @@
         <v>400</v>
       </c>
       <c r="M43" s="3">
+        <v>400</v>
+      </c>
+      <c r="N43" s="3">
         <v>300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>200</v>
-      </c>
-      <c r="O43" s="3">
-        <v>500</v>
       </c>
       <c r="P43" s="3">
         <v>500</v>
@@ -3027,8 +3120,8 @@
       <c r="R43" s="3">
         <v>500</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>3</v>
+      <c r="S43" s="3">
+        <v>500</v>
       </c>
       <c r="T43" s="3" t="s">
         <v>3</v>
@@ -3042,8 +3135,8 @@
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X43" s="3">
-        <v>0</v>
+      <c r="X43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y43" s="3">
         <v>0</v>
@@ -3051,22 +3144,25 @@
       <c r="Z43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E44" s="3">
         <v>1800</v>
-      </c>
-      <c r="E44" s="3">
-        <v>1100</v>
       </c>
       <c r="F44" s="3">
         <v>1100</v>
       </c>
-      <c r="G44" s="3" t="s">
-        <v>3</v>
+      <c r="G44" s="3">
+        <v>1100</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>3</v>
@@ -3080,8 +3176,8 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -3125,61 +3221,64 @@
       <c r="Z44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="E45" s="3">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="F45" s="3">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="G45" s="3">
+        <v>400</v>
+      </c>
+      <c r="H45" s="3">
+        <v>600</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K45" s="3">
+        <v>500</v>
+      </c>
+      <c r="L45" s="3">
+        <v>900</v>
+      </c>
+      <c r="M45" s="3">
         <v>1300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="N45" s="3">
+        <v>200</v>
+      </c>
+      <c r="O45" s="3">
         <v>1300</v>
       </c>
-      <c r="I45" s="3">
-        <v>700</v>
-      </c>
-      <c r="J45" s="3">
-        <v>500</v>
-      </c>
-      <c r="K45" s="3">
-        <v>900</v>
-      </c>
-      <c r="L45" s="3">
-        <v>1300</v>
-      </c>
-      <c r="M45" s="3">
-        <v>200</v>
-      </c>
-      <c r="N45" s="3">
-        <v>1300</v>
-      </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1900</v>
-      </c>
-      <c r="R45" s="3">
-        <v>700</v>
       </c>
       <c r="S45" s="3">
         <v>700</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>3</v>
+      <c r="T45" s="3">
+        <v>700</v>
       </c>
       <c r="U45" s="3" t="s">
         <v>3</v>
@@ -3199,62 +3298,65 @@
       <c r="Z45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>14000</v>
+      </c>
+      <c r="E46" s="3">
         <v>19700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>8500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>9200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>16100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>15200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>11600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>18100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>23000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>28200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>35100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>41000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>44700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>49200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>6900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>8300</v>
       </c>
-      <c r="T46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3273,59 +3375,62 @@
       <c r="Z46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>100</v>
-      </c>
-      <c r="E47" s="3">
-        <v>100</v>
-      </c>
-      <c r="F47" s="3">
-        <v>200</v>
-      </c>
-      <c r="G47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K47" s="3">
         <v>700</v>
-      </c>
-      <c r="H47" s="3">
-        <v>700</v>
-      </c>
-      <c r="I47" s="3">
-        <v>700</v>
-      </c>
-      <c r="J47" s="3">
-        <v>700</v>
-      </c>
-      <c r="K47" s="3">
-        <v>400</v>
       </c>
       <c r="L47" s="3">
         <v>400</v>
       </c>
       <c r="M47" s="3">
+        <v>400</v>
+      </c>
+      <c r="N47" s="3">
         <v>500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>600</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
       <c r="P47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3">
         <v>100</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>100</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3338,8 +3443,8 @@
       <c r="W47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X47" s="3">
-        <v>0</v>
+      <c r="X47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y47" s="3">
         <v>0</v>
@@ -3347,13 +3452,16 @@
       <c r="Z47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="E48" s="3">
         <v>300</v>
@@ -3362,10 +3470,10 @@
         <v>300</v>
       </c>
       <c r="G48" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="H48" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="I48" s="3">
         <v>400</v>
@@ -3374,7 +3482,7 @@
         <v>400</v>
       </c>
       <c r="K48" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="L48" s="3">
         <v>500</v>
@@ -3389,19 +3497,19 @@
         <v>500</v>
       </c>
       <c r="P48" s="3">
+        <v>500</v>
+      </c>
+      <c r="Q48" s="3">
         <v>300</v>
       </c>
-      <c r="Q48" s="3">
-        <v>0</v>
-      </c>
       <c r="R48" s="3">
         <v>0</v>
       </c>
       <c r="S48" s="3">
         <v>0</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>3</v>
+      <c r="T48" s="3">
+        <v>0</v>
       </c>
       <c r="U48" s="3" t="s">
         <v>3</v>
@@ -3421,8 +3529,11 @@
       <c r="Z48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3495,8 +3606,11 @@
       <c r="Z49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3569,8 +3683,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3643,8 +3760,11 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3652,22 +3772,22 @@
         <v>800</v>
       </c>
       <c r="E52" s="3">
-        <v>300</v>
+        <v>900</v>
       </c>
       <c r="F52" s="3">
         <v>400</v>
       </c>
       <c r="G52" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="H52" s="3">
-        <v>400</v>
+        <v>800</v>
       </c>
       <c r="I52" s="3">
-        <v>400</v>
+        <v>1100</v>
       </c>
       <c r="J52" s="3">
-        <v>500</v>
+        <v>1100</v>
       </c>
       <c r="K52" s="3">
         <v>500</v>
@@ -3676,13 +3796,13 @@
         <v>500</v>
       </c>
       <c r="M52" s="3">
+        <v>500</v>
+      </c>
+      <c r="N52" s="3">
         <v>400</v>
       </c>
-      <c r="N52" s="3">
-        <v>0</v>
-      </c>
       <c r="O52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P52" s="3">
         <v>100</v>
@@ -3691,14 +3811,14 @@
         <v>100</v>
       </c>
       <c r="R52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S52" s="3">
+        <v>0</v>
+      </c>
+      <c r="T52" s="3">
         <v>400</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3717,8 +3837,11 @@
       <c r="Z52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3791,62 +3914,65 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>15100</v>
+      </c>
+      <c r="E54" s="3">
         <v>20800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>9400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>10600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>17600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>16800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>13200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>19500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>24400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>29600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>36300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>41600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>45100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>49400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>7100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>8700</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3865,8 +3991,11 @@
       <c r="Z54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3893,8 +4022,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3921,61 +4051,62 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E57" s="3">
         <v>1500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>500</v>
-      </c>
-      <c r="J57" s="3">
-        <v>600</v>
       </c>
       <c r="K57" s="3">
         <v>600</v>
       </c>
       <c r="L57" s="3">
+        <v>600</v>
+      </c>
+      <c r="M57" s="3">
         <v>800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>400</v>
-      </c>
-      <c r="R57" s="3">
-        <v>200</v>
       </c>
       <c r="S57" s="3">
         <v>200</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>3</v>
+      <c r="T57" s="3">
+        <v>200</v>
       </c>
       <c r="U57" s="3" t="s">
         <v>3</v>
@@ -3995,37 +4126,40 @@
       <c r="Z57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="E58" s="3">
+        <v>100</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
+        <v>200</v>
+      </c>
+      <c r="G58" s="3">
+        <v>200</v>
+      </c>
+      <c r="H58" s="3">
+        <v>200</v>
+      </c>
+      <c r="I58" s="3">
+        <v>200</v>
+      </c>
+      <c r="J58" s="3">
+        <v>200</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
+      <c r="L58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M58" s="3">
         <v>0</v>
@@ -4040,16 +4174,16 @@
         <v>0</v>
       </c>
       <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3">
         <v>300</v>
-      </c>
-      <c r="R58" s="3">
-        <v>200</v>
       </c>
       <c r="S58" s="3">
         <v>200</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>3</v>
+      <c r="T58" s="3">
+        <v>200</v>
       </c>
       <c r="U58" s="3" t="s">
         <v>3</v>
@@ -4069,62 +4203,65 @@
       <c r="Z58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1900</v>
+        <v>300</v>
       </c>
       <c r="E59" s="3">
+        <v>300</v>
+      </c>
+      <c r="F59" s="3">
+        <v>900</v>
+      </c>
+      <c r="G59" s="3">
+        <v>1600</v>
+      </c>
+      <c r="H59" s="3">
+        <v>200</v>
+      </c>
+      <c r="I59" s="3">
+        <v>300</v>
+      </c>
+      <c r="J59" s="3">
+        <v>200</v>
+      </c>
+      <c r="K59" s="3">
+        <v>4400</v>
+      </c>
+      <c r="L59" s="3">
+        <v>3700</v>
+      </c>
+      <c r="M59" s="3">
         <v>2600</v>
       </c>
-      <c r="F59" s="3">
-        <v>2800</v>
-      </c>
-      <c r="G59" s="3">
-        <v>3600</v>
-      </c>
-      <c r="H59" s="3">
-        <v>3000</v>
-      </c>
-      <c r="I59" s="3">
-        <v>4800</v>
-      </c>
-      <c r="J59" s="3">
-        <v>4400</v>
-      </c>
-      <c r="K59" s="3">
-        <v>3700</v>
-      </c>
-      <c r="L59" s="3">
-        <v>2600</v>
-      </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>500</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4143,62 +4280,65 @@
       <c r="Z59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E60" s="3">
         <v>3400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>6600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>5900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>5500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>4600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>5300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>5000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>800</v>
       </c>
-      <c r="T60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4217,16 +4357,19 @@
       <c r="Z60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="F61" s="3">
         <v>0</v>
@@ -4235,13 +4378,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -4265,14 +4408,14 @@
         <v>0</v>
       </c>
       <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3">
         <v>11400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>11100</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
         <v>0</v>
       </c>
@@ -4291,13 +4434,16 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="E62" s="3">
         <v>0</v>
@@ -4309,28 +4455,28 @@
         <v>100</v>
       </c>
       <c r="H62" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I62" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="J62" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="K62" s="3">
         <v>400</v>
       </c>
       <c r="L62" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="M62" s="3">
         <v>500</v>
       </c>
       <c r="N62" s="3">
+        <v>500</v>
+      </c>
+      <c r="O62" s="3">
         <v>300</v>
-      </c>
-      <c r="O62" s="3">
-        <v>400</v>
       </c>
       <c r="P62" s="3">
         <v>400</v>
@@ -4339,14 +4485,14 @@
         <v>400</v>
       </c>
       <c r="R62" s="3">
+        <v>400</v>
+      </c>
+      <c r="S62" s="3">
         <v>2500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>700</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4365,8 +4511,11 @@
       <c r="Z62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4439,8 +4588,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4513,8 +4665,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4587,62 +4742,65 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E66" s="3">
         <v>4000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>6600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>6000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>15100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>12600</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4661,8 +4819,11 @@
       <c r="Z66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4689,8 +4850,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4763,8 +4925,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4837,8 +5002,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4885,14 +5053,14 @@
         <v>0</v>
       </c>
       <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3">
         <v>32800</v>
       </c>
-      <c r="S70" s="3">
+      <c r="T70" s="3">
         <v>30300</v>
       </c>
-      <c r="T70" s="3">
-        <v>0</v>
-      </c>
       <c r="U70" s="3">
         <v>0</v>
       </c>
@@ -4911,8 +5079,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4985,62 +5156,65 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-143500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-136300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-130100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-124400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-118400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-109500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-102200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-95100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-87200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-78600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-71700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-64800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-58500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-53300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-48600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-40900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-34200</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5059,8 +5233,11 @@
       <c r="Z72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5133,8 +5310,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5207,8 +5387,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5281,62 +5464,65 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>10300</v>
+      </c>
+      <c r="E76" s="3">
         <v>16800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-1500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>12800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>11100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>7900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>14700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>20500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>26500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>32700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>38400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>43000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>47300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-40900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-34200</v>
       </c>
-      <c r="T76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5355,8 +5541,11 @@
       <c r="Z76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5429,73 +5618,76 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5508,68 +5700,71 @@
       <c r="Z80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-6200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-5700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-6000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-9000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-7300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-7100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-7900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-8600</v>
-      </c>
-      <c r="L81" s="3">
-        <v>-6900</v>
       </c>
       <c r="M81" s="3">
         <v>-6900</v>
       </c>
       <c r="N81" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="O81" s="3">
         <v>-6300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-5200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-4700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-8100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-7400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-14500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-4900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-4000</v>
       </c>
-      <c r="V81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5582,8 +5777,11 @@
       <c r="Z81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5610,8 +5808,9 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5619,7 +5818,7 @@
         <v>0</v>
       </c>
       <c r="E83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F83" s="3">
         <v>0</v>
@@ -5669,8 +5868,8 @@
       <c r="U83" s="3">
         <v>0</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>3</v>
+      <c r="V83" s="3">
+        <v>0</v>
       </c>
       <c r="W83" s="3" t="s">
         <v>3</v>
@@ -5684,8 +5883,11 @@
       <c r="Z83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5758,8 +5960,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5832,8 +6037,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5906,8 +6114,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5980,8 +6191,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6054,67 +6268,70 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-8200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-4100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-5200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-7000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-7900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-6100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-6300</v>
-      </c>
-      <c r="K89" s="3">
-        <v>-6400</v>
       </c>
       <c r="L89" s="3">
         <v>-6400</v>
       </c>
       <c r="M89" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="N89" s="3">
         <v>-5800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-5100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-3300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-3700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-4000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-2500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-8100</v>
-      </c>
-      <c r="T89" s="3">
-        <v>-2200</v>
       </c>
       <c r="U89" s="3">
         <v>-2200</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>3</v>
+      <c r="V89" s="3">
+        <v>-2200</v>
       </c>
       <c r="W89" s="3" t="s">
         <v>3</v>
@@ -6128,8 +6345,11 @@
       <c r="Z89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6156,8 +6376,9 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6192,19 +6413,19 @@
         <v>0</v>
       </c>
       <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
         <v>-200</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
       <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-300</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
-      <c r="R91" s="3" t="s">
-        <v>3</v>
+      <c r="R91" s="3">
+        <v>0</v>
       </c>
       <c r="S91" s="3" t="s">
         <v>3</v>
@@ -6221,8 +6442,8 @@
       <c r="W91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X91" s="3">
-        <v>0</v>
+      <c r="X91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y91" s="3">
         <v>0</v>
@@ -6230,8 +6451,11 @@
       <c r="Z91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6304,8 +6528,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6378,8 +6605,11 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -6402,29 +6632,29 @@
         <v>0</v>
       </c>
       <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
         <v>800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>3400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>5000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>6500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>5900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-8900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-13700</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
       <c r="R94" s="3">
         <v>0</v>
       </c>
@@ -6437,8 +6667,8 @@
       <c r="U94" s="3">
         <v>0</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>3</v>
+      <c r="V94" s="3">
+        <v>0</v>
       </c>
       <c r="W94" s="3" t="s">
         <v>3</v>
@@ -6452,8 +6682,11 @@
       <c r="Z94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6480,31 +6713,32 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -6554,8 +6788,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6628,8 +6865,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6702,8 +6942,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6776,68 +7019,71 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>100</v>
+      </c>
+      <c r="E100" s="3">
         <v>22900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>3700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>8100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>9600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1900</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
         <v>0</v>
       </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>-200</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
       <c r="P100" s="3">
         <v>0</v>
       </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>45100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>11400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>7000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>1200</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6850,31 +7096,34 @@
       <c r="Z100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -6924,68 +7173,71 @@
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="E102" s="3">
         <v>14700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-4000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-6800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>3500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-5200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-12200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-17400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>41000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-1900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>3300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>4700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-1000</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6996,6 +7248,9 @@
         <v>3</v>
       </c>
       <c r="Z102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MOVE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MOVE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="92">
   <si>
     <t>MOVE</t>
   </si>
@@ -656,105 +656,105 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
@@ -767,23 +767,26 @@
       <c r="AA7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F8" s="3">
+      <c r="D8" s="3">
+        <v>100</v>
+      </c>
+      <c r="E8" s="3">
+        <v>100</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G8" s="3">
         <v>900</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H8" s="3" t="s">
         <v>3</v>
       </c>
@@ -799,8 +802,8 @@
       <c r="L8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M8" s="3">
-        <v>0</v>
+      <c r="M8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N8" s="3">
         <v>0</v>
@@ -844,23 +847,26 @@
       <c r="AA8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>600</v>
+      </c>
+      <c r="E9" s="3">
         <v>800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1200</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H9" s="3" t="s">
         <v>3</v>
       </c>
@@ -921,22 +927,25 @@
       <c r="AA9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E10" s="3">
         <v>-800</v>
-      </c>
-      <c r="E10" s="3">
-        <v>-400</v>
       </c>
       <c r="F10" s="3">
         <v>-400</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
+      <c r="G10" s="3">
+        <v>-400</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>3</v>
@@ -998,8 +1007,11 @@
       <c r="AA10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1027,71 +1039,72 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E12" s="3">
         <v>3400</v>
-      </c>
-      <c r="E12" s="3">
-        <v>2900</v>
       </c>
       <c r="F12" s="3">
         <v>2900</v>
       </c>
       <c r="G12" s="3">
-        <v>3100</v>
+        <v>2900</v>
       </c>
       <c r="H12" s="3">
+        <v>2900</v>
+      </c>
+      <c r="I12" s="3">
         <v>5600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>4200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>3900</v>
-      </c>
-      <c r="K12" s="3">
-        <v>5100</v>
       </c>
       <c r="L12" s="3">
         <v>5100</v>
       </c>
       <c r="M12" s="3">
+        <v>5100</v>
+      </c>
+      <c r="N12" s="3">
         <v>4100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>4600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>4500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>3800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>3200</v>
-      </c>
-      <c r="R12" s="3">
-        <v>1900</v>
       </c>
       <c r="S12" s="3">
         <v>1900</v>
       </c>
       <c r="T12" s="3">
+        <v>1900</v>
+      </c>
+      <c r="U12" s="3">
         <v>6500</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>2300</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>1500</v>
       </c>
-      <c r="W12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1104,8 +1117,11 @@
       <c r="AA12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1181,8 +1197,11 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1207,8 +1226,8 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1216,21 +1235,21 @@
       <c r="M14" s="3">
         <v>0</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>-400</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1246,8 +1265,8 @@
       <c r="W14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
+      <c r="X14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y14" s="3">
         <v>0</v>
@@ -1258,8 +1277,11 @@
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1270,11 +1292,11 @@
         <v>0</v>
       </c>
       <c r="F15" s="3">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3">
         <v>100</v>
       </c>
-      <c r="G15" s="3">
-        <v>0</v>
-      </c>
       <c r="H15" s="3">
         <v>0</v>
       </c>
@@ -1335,8 +1357,11 @@
       <c r="AA15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1361,71 +1386,72 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E17" s="3">
         <v>7400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>6400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>6600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>6000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>9100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>7400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>7200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>8000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>8700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>6800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>6900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>6300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>5200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>4700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>7900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2000</v>
       </c>
-      <c r="W17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1438,71 +1464,74 @@
       <c r="AA17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="E18" s="3">
         <v>-7400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-6400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-5800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-6000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-9100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-7400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-7200</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M18" s="3">
+      <c r="M18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N18" s="3">
         <v>-6800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-6900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-6300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-5200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-4700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-3300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-3200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-7900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-2700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-2000</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1515,8 +1544,11 @@
       <c r="AA18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1544,8 +1576,9 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1576,8 +1609,8 @@
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
+      <c r="M20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N20" s="3">
         <v>0</v>
@@ -1592,22 +1625,22 @@
         <v>0</v>
       </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>-1500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>200</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
-      <c r="W20" s="3" t="s">
-        <v>3</v>
+      <c r="W20" s="3">
+        <v>0</v>
       </c>
       <c r="X20" s="3" t="s">
         <v>3</v>
@@ -1621,71 +1654,74 @@
       <c r="AA20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="E21" s="3">
         <v>-7300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-6400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-5700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-6000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-9000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-7300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-7200</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N21" s="3">
         <v>-6800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-6900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-6300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-5200</v>
-      </c>
-      <c r="Q21" s="3">
-        <v>-4700</v>
       </c>
       <c r="R21" s="3">
         <v>-4700</v>
       </c>
       <c r="S21" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="T21" s="3">
         <v>-4500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-7500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-2600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-2000</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1698,8 +1734,11 @@
       <c r="AA21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1724,8 +1763,8 @@
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1746,22 +1785,22 @@
         <v>0</v>
       </c>
       <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3">
         <v>900</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>500</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>600</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>200</v>
       </c>
-      <c r="V22" s="3">
-        <v>0</v>
-      </c>
-      <c r="W22" s="3" t="s">
-        <v>3</v>
+      <c r="W22" s="3">
+        <v>0</v>
       </c>
       <c r="X22" s="3" t="s">
         <v>3</v>
@@ -1775,71 +1814,74 @@
       <c r="AA22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-7200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-6200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-5700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-6000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-9000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-7300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-7100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-7900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-8600</v>
-      </c>
-      <c r="M23" s="3">
-        <v>-6900</v>
       </c>
       <c r="N23" s="3">
         <v>-6900</v>
       </c>
       <c r="O23" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="P23" s="3">
         <v>-6300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-5200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-4700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-5600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-4900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-8100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-2700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-2000</v>
       </c>
-      <c r="W23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1852,8 +1894,11 @@
       <c r="AA23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1878,8 +1923,8 @@
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L24" s="3">
         <v>0</v>
@@ -1929,8 +1974,11 @@
       <c r="AA24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2006,71 +2054,74 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-7200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-6200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-5700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-6000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-9000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-7300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-7100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-7900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-8600</v>
-      </c>
-      <c r="M26" s="3">
-        <v>-6900</v>
       </c>
       <c r="N26" s="3">
         <v>-6900</v>
       </c>
       <c r="O26" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="P26" s="3">
         <v>-6300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-5200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-4700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-5600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-4900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-8100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-2700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-2000</v>
       </c>
-      <c r="W26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2083,71 +2134,74 @@
       <c r="AA26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-7200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-6200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-5700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-6000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-9000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-7300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-7100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-7900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-8600</v>
-      </c>
-      <c r="M27" s="3">
-        <v>-6900</v>
       </c>
       <c r="N27" s="3">
         <v>-6900</v>
       </c>
       <c r="O27" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="P27" s="3">
         <v>-6300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-5200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-4700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-8100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-7400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-14500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-4900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-4000</v>
       </c>
-      <c r="W27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2160,8 +2214,11 @@
       <c r="AA27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2237,8 +2294,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2314,8 +2374,11 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2391,8 +2454,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2468,8 +2534,11 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2500,8 +2569,8 @@
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
+      <c r="M32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N32" s="3">
         <v>0</v>
@@ -2516,22 +2585,22 @@
         <v>0</v>
       </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>1500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-200</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
-      <c r="W32" s="3" t="s">
-        <v>3</v>
+      <c r="W32" s="3">
+        <v>0</v>
       </c>
       <c r="X32" s="3" t="s">
         <v>3</v>
@@ -2545,71 +2614,74 @@
       <c r="AA32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-7200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-6200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-5700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-6000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-9000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-7300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-7100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-7900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-8600</v>
-      </c>
-      <c r="M33" s="3">
-        <v>-6900</v>
       </c>
       <c r="N33" s="3">
         <v>-6900</v>
       </c>
       <c r="O33" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="P33" s="3">
         <v>-6300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-5200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-4700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-8100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-7400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-14500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-4900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-4000</v>
       </c>
-      <c r="W33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2622,8 +2694,11 @@
       <c r="AA33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2699,71 +2774,74 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-7200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-6200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-5700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-6000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-9000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-7300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-7100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-7900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-8600</v>
-      </c>
-      <c r="M35" s="3">
-        <v>-6900</v>
       </c>
       <c r="N35" s="3">
         <v>-6900</v>
       </c>
       <c r="O35" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="P35" s="3">
         <v>-6300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-5200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-4700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-8100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-7400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-14500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-4900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-4000</v>
       </c>
-      <c r="W35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2776,76 +2854,79 @@
       <c r="AA35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2858,8 +2939,11 @@
       <c r="AA38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2887,8 +2971,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2916,65 +3001,66 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>7900</v>
+      </c>
+      <c r="E41" s="3">
         <v>11300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>16900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>6100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>7700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>14500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>14300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>10800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>15900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>17100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>18400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>17700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>17100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>29300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>46800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>5700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>7600</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2993,8 +3079,11 @@
       <c r="AA41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3023,26 +3112,26 @@
         <v>0</v>
       </c>
       <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
         <v>800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>4200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>9200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>15900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>22200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>13400</v>
       </c>
-      <c r="R42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3058,8 +3147,8 @@
       <c r="W42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X42" s="3">
-        <v>0</v>
+      <c r="X42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y42" s="3">
         <v>0</v>
@@ -3070,25 +3159,28 @@
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E43" s="3">
         <v>200</v>
       </c>
       <c r="F43" s="3">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="G43" s="3">
         <v>500</v>
       </c>
       <c r="H43" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="I43" s="3">
         <v>300</v>
@@ -3097,7 +3189,7 @@
         <v>300</v>
       </c>
       <c r="K43" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="L43" s="3">
         <v>400</v>
@@ -3106,13 +3198,13 @@
         <v>400</v>
       </c>
       <c r="N43" s="3">
+        <v>400</v>
+      </c>
+      <c r="O43" s="3">
         <v>300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>200</v>
-      </c>
-      <c r="P43" s="3">
-        <v>500</v>
       </c>
       <c r="Q43" s="3">
         <v>500</v>
@@ -3123,8 +3215,8 @@
       <c r="S43" s="3">
         <v>500</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>3</v>
+      <c r="T43" s="3">
+        <v>500</v>
       </c>
       <c r="U43" s="3" t="s">
         <v>3</v>
@@ -3138,8 +3230,8 @@
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y43" s="3">
-        <v>0</v>
+      <c r="Y43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z43" s="3">
         <v>0</v>
@@ -3147,8 +3239,11 @@
       <c r="AA43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3156,16 +3251,16 @@
         <v>2000</v>
       </c>
       <c r="E44" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F44" s="3">
         <v>1800</v>
-      </c>
-      <c r="F44" s="3">
-        <v>1100</v>
       </c>
       <c r="G44" s="3">
         <v>1100</v>
       </c>
-      <c r="H44" s="3" t="s">
-        <v>3</v>
+      <c r="H44" s="3">
+        <v>1100</v>
       </c>
       <c r="I44" s="3" t="s">
         <v>3</v>
@@ -3179,8 +3274,8 @@
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -3224,8 +3319,11 @@
       <c r="AA44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3236,52 +3334,52 @@
         <v>0</v>
       </c>
       <c r="F45" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="G45" s="3">
         <v>400</v>
       </c>
       <c r="H45" s="3">
+        <v>400</v>
+      </c>
+      <c r="I45" s="3">
         <v>600</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3">
         <v>500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1900</v>
-      </c>
-      <c r="S45" s="3">
-        <v>700</v>
       </c>
       <c r="T45" s="3">
         <v>700</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>3</v>
+      <c r="U45" s="3">
+        <v>700</v>
       </c>
       <c r="V45" s="3" t="s">
         <v>3</v>
@@ -3301,65 +3399,68 @@
       <c r="AA45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E46" s="3">
         <v>14000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>19700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>8500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>9200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>16100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>15200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>11600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>18100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>23000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>28200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>35100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>41000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>44700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>49200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>6900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>8300</v>
       </c>
-      <c r="U46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3378,8 +3479,11 @@
       <c r="AA46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3404,36 +3508,36 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
+      <c r="K47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L47" s="3">
         <v>700</v>
-      </c>
-      <c r="L47" s="3">
-        <v>400</v>
       </c>
       <c r="M47" s="3">
         <v>400</v>
       </c>
       <c r="N47" s="3">
+        <v>400</v>
+      </c>
+      <c r="O47" s="3">
         <v>500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>600</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
-      </c>
       <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3">
         <v>100</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>100</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3446,8 +3550,8 @@
       <c r="X47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y47" s="3">
-        <v>0</v>
+      <c r="Y47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z47" s="3">
         <v>0</v>
@@ -3455,28 +3559,31 @@
       <c r="AA47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>800</v>
+      </c>
+      <c r="E48" s="3">
         <v>200</v>
-      </c>
-      <c r="E48" s="3">
-        <v>300</v>
       </c>
       <c r="F48" s="3">
         <v>300</v>
       </c>
       <c r="G48" s="3">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="H48" s="3">
         <v>600</v>
       </c>
       <c r="I48" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="J48" s="3">
         <v>400</v>
@@ -3485,7 +3592,7 @@
         <v>400</v>
       </c>
       <c r="L48" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="M48" s="3">
         <v>500</v>
@@ -3500,19 +3607,19 @@
         <v>500</v>
       </c>
       <c r="Q48" s="3">
+        <v>500</v>
+      </c>
+      <c r="R48" s="3">
         <v>300</v>
       </c>
-      <c r="R48" s="3">
-        <v>0</v>
-      </c>
       <c r="S48" s="3">
         <v>0</v>
       </c>
       <c r="T48" s="3">
         <v>0</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>3</v>
+      <c r="U48" s="3">
+        <v>0</v>
       </c>
       <c r="V48" s="3" t="s">
         <v>3</v>
@@ -3532,8 +3639,11 @@
       <c r="AA48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3609,8 +3719,11 @@
       <c r="AA49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3686,8 +3799,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3763,34 +3879,37 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>100</v>
+      </c>
+      <c r="E52" s="3">
         <v>800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>800</v>
-      </c>
-      <c r="I52" s="3">
-        <v>1100</v>
       </c>
       <c r="J52" s="3">
         <v>1100</v>
       </c>
       <c r="K52" s="3">
-        <v>500</v>
+        <v>1100</v>
       </c>
       <c r="L52" s="3">
         <v>500</v>
@@ -3799,13 +3918,13 @@
         <v>500</v>
       </c>
       <c r="N52" s="3">
+        <v>500</v>
+      </c>
+      <c r="O52" s="3">
         <v>400</v>
       </c>
-      <c r="O52" s="3">
-        <v>0</v>
-      </c>
       <c r="P52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q52" s="3">
         <v>100</v>
@@ -3814,14 +3933,14 @@
         <v>100</v>
       </c>
       <c r="S52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T52" s="3">
+        <v>0</v>
+      </c>
+      <c r="U52" s="3">
         <v>400</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3840,8 +3959,11 @@
       <c r="AA52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3917,65 +4039,68 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>11300</v>
+      </c>
+      <c r="E54" s="3">
         <v>15100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>20800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>9400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>10600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>17600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>16800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>13200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>19500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>24400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>29600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>36300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>41600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>45100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>49400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>7100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>8700</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3994,8 +4119,11 @@
       <c r="AA54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4023,8 +4151,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4052,64 +4181,65 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E57" s="3">
         <v>1900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>500</v>
-      </c>
-      <c r="K57" s="3">
-        <v>600</v>
       </c>
       <c r="L57" s="3">
         <v>600</v>
       </c>
       <c r="M57" s="3">
+        <v>600</v>
+      </c>
+      <c r="N57" s="3">
         <v>800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>400</v>
-      </c>
-      <c r="S57" s="3">
-        <v>200</v>
       </c>
       <c r="T57" s="3">
         <v>200</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>3</v>
+      <c r="U57" s="3">
+        <v>200</v>
       </c>
       <c r="V57" s="3" t="s">
         <v>3</v>
@@ -4129,19 +4259,22 @@
       <c r="AA57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E58" s="3">
         <v>100</v>
       </c>
       <c r="F58" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G58" s="3">
         <v>200</v>
@@ -4155,14 +4288,14 @@
       <c r="J58" s="3">
         <v>200</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
+      <c r="K58" s="3">
+        <v>200</v>
       </c>
       <c r="L58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
+      <c r="M58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N58" s="3">
         <v>0</v>
@@ -4177,16 +4310,16 @@
         <v>0</v>
       </c>
       <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3">
         <v>300</v>
-      </c>
-      <c r="S58" s="3">
-        <v>200</v>
       </c>
       <c r="T58" s="3">
         <v>200</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>3</v>
+      <c r="U58" s="3">
+        <v>200</v>
       </c>
       <c r="V58" s="3" t="s">
         <v>3</v>
@@ -4206,65 +4339,68 @@
       <c r="AA58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="E59" s="3">
         <v>300</v>
       </c>
       <c r="F59" s="3">
+        <v>300</v>
+      </c>
+      <c r="G59" s="3">
         <v>900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>4400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>3700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>500</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4283,65 +4419,68 @@
       <c r="AA59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E60" s="3">
         <v>4200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>6600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>5900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>5500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>4600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>5300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>5000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>800</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4360,35 +4499,38 @@
       <c r="AA60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="E61" s="3">
         <v>600</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="G61" s="3">
         <v>0</v>
       </c>
       <c r="H61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I61" s="3">
         <v>100</v>
       </c>
       <c r="J61" s="3">
+        <v>100</v>
+      </c>
+      <c r="K61" s="3">
         <v>200</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -4411,14 +4553,14 @@
         <v>0</v>
       </c>
       <c r="S61" s="3">
+        <v>0</v>
+      </c>
+      <c r="T61" s="3">
         <v>11400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>11100</v>
       </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
       <c r="V61" s="3">
         <v>0</v>
       </c>
@@ -4437,8 +4579,11 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4452,34 +4597,34 @@
         <v>0</v>
       </c>
       <c r="G62" s="3">
+        <v>0</v>
+      </c>
+      <c r="H62" s="3">
         <v>100</v>
       </c>
-      <c r="H62" s="3">
-        <v>0</v>
-      </c>
       <c r="I62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J62" s="3">
         <v>100</v>
       </c>
       <c r="K62" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="L62" s="3">
         <v>400</v>
       </c>
       <c r="M62" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="N62" s="3">
         <v>500</v>
       </c>
       <c r="O62" s="3">
+        <v>500</v>
+      </c>
+      <c r="P62" s="3">
         <v>300</v>
-      </c>
-      <c r="P62" s="3">
-        <v>400</v>
       </c>
       <c r="Q62" s="3">
         <v>400</v>
@@ -4488,14 +4633,14 @@
         <v>400</v>
       </c>
       <c r="S62" s="3">
+        <v>400</v>
+      </c>
+      <c r="T62" s="3">
         <v>2500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>700</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4514,8 +4659,11 @@
       <c r="AA62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4591,8 +4739,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4668,8 +4819,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4745,65 +4899,68 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E66" s="3">
         <v>4800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>6600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>6000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>15100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>12600</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4822,8 +4979,11 @@
       <c r="AA66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4851,8 +5011,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4928,8 +5089,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5005,8 +5169,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5056,14 +5223,14 @@
         <v>0</v>
       </c>
       <c r="S70" s="3">
+        <v>0</v>
+      </c>
+      <c r="T70" s="3">
         <v>32800</v>
       </c>
-      <c r="T70" s="3">
+      <c r="U70" s="3">
         <v>30300</v>
       </c>
-      <c r="U70" s="3">
-        <v>0</v>
-      </c>
       <c r="V70" s="3">
         <v>0</v>
       </c>
@@ -5082,8 +5249,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5159,65 +5329,68 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-148100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-143500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-136300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-130100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-124400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-118400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-109500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-102200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-95100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-87200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-78600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-71700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-64800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-58500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-53300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-48600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-40900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-34200</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5236,8 +5409,11 @@
       <c r="AA72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5313,8 +5489,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5390,8 +5569,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5467,65 +5649,68 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E76" s="3">
         <v>10300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>16800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-1500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>12800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>11100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>7900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>14700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>20500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>26500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>32700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>38400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>43000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>47300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-40900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-34200</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5544,8 +5729,11 @@
       <c r="AA76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5621,76 +5809,79 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5703,71 +5894,74 @@
       <c r="AA80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-7200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-6200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-5700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-6000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-9000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-7300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-7100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-7900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-8600</v>
-      </c>
-      <c r="M81" s="3">
-        <v>-6900</v>
       </c>
       <c r="N81" s="3">
         <v>-6900</v>
       </c>
       <c r="O81" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="P81" s="3">
         <v>-6300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-5200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-4700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-8100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-7400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-14500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-4900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-4000</v>
       </c>
-      <c r="W81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5780,8 +5974,11 @@
       <c r="AA81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5809,8 +6006,9 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5871,8 +6069,8 @@
       <c r="V83" s="3">
         <v>0</v>
       </c>
-      <c r="W83" s="3" t="s">
-        <v>3</v>
+      <c r="W83" s="3">
+        <v>0</v>
       </c>
       <c r="X83" s="3" t="s">
         <v>3</v>
@@ -5886,8 +6084,11 @@
       <c r="AA83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5963,8 +6164,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6040,8 +6244,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6117,8 +6324,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6194,8 +6404,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6271,70 +6484,73 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-5700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-8200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-4100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-5200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-7000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-7900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-6100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-6300</v>
-      </c>
-      <c r="L89" s="3">
-        <v>-6400</v>
       </c>
       <c r="M89" s="3">
         <v>-6400</v>
       </c>
       <c r="N89" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="O89" s="3">
         <v>-5800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-5100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-3700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-4000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-2500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-8100</v>
-      </c>
-      <c r="U89" s="3">
-        <v>-2200</v>
       </c>
       <c r="V89" s="3">
         <v>-2200</v>
       </c>
-      <c r="W89" s="3" t="s">
-        <v>3</v>
+      <c r="W89" s="3">
+        <v>-2200</v>
       </c>
       <c r="X89" s="3" t="s">
         <v>3</v>
@@ -6348,8 +6564,11 @@
       <c r="AA89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6377,8 +6596,9 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6416,19 +6636,19 @@
         <v>0</v>
       </c>
       <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
         <v>-200</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
       <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
         <v>-300</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
-      <c r="S91" s="3" t="s">
-        <v>3</v>
+      <c r="S91" s="3">
+        <v>0</v>
       </c>
       <c r="T91" s="3" t="s">
         <v>3</v>
@@ -6445,8 +6665,8 @@
       <c r="X91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y91" s="3">
-        <v>0</v>
+      <c r="Y91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z91" s="3">
         <v>0</v>
@@ -6454,8 +6674,11 @@
       <c r="AA91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6531,8 +6754,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6608,8 +6834,11 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -6635,29 +6864,29 @@
         <v>0</v>
       </c>
       <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
         <v>800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>3400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>5000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>6500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>5900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-8900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-13700</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
       <c r="S94" s="3">
         <v>0</v>
       </c>
@@ -6670,8 +6899,8 @@
       <c r="V94" s="3">
         <v>0</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>3</v>
+      <c r="W94" s="3">
+        <v>0</v>
       </c>
       <c r="X94" s="3" t="s">
         <v>3</v>
@@ -6685,8 +6914,11 @@
       <c r="AA94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6714,8 +6946,9 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6740,8 +6973,8 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -6791,8 +7024,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6868,8 +7104,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6945,8 +7184,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7022,71 +7264,74 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E100" s="3">
         <v>100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>22900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>3700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>8100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>9600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1900</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
       <c r="N100" s="3">
         <v>0</v>
       </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>-200</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
       <c r="Q100" s="3">
         <v>0</v>
       </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>45100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>11400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>7000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>1200</v>
       </c>
-      <c r="W100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7099,8 +7344,11 @@
       <c r="AA100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7125,8 +7373,8 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -7176,71 +7424,74 @@
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-5600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>14700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-4000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-6800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>3500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-5200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-12200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-17400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>41000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-1900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>3300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>4700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-1000</v>
       </c>
-      <c r="W102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
@@ -7251,6 +7502,9 @@
         <v>3</v>
       </c>
       <c r="AA102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
